--- a/data/midwifery_center/data.xlsx
+++ b/data/midwifery_center/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\itfile01\保健医療政策課\オープンデータ\助産所(0115）\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\userdata\52845\デスクトップ\五藤\2. オープンデータ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6228AC97-5AF3-4BDF-9AFD-4A36D9A47E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5D6BEA-5A5A-491F-84EA-98290C9199B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="122">
   <si>
     <t>№</t>
   </si>
@@ -58,60 +58,60 @@
     <t>name</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>特定非営利活動法人いのちの応援舎ぼっこ助産院</t>
+  </si>
+  <si>
+    <t>理事長　松尾　真理</t>
+  </si>
+  <si>
+    <t>特定非営利活動法人いのちの応援舎　</t>
+  </si>
+  <si>
+    <t>34.332435</t>
+  </si>
+  <si>
+    <t>134.097244</t>
+  </si>
+  <si>
+    <t>香川県高松市春日町１１７６番地</t>
+  </si>
+  <si>
+    <t>087-844-4103</t>
+  </si>
+  <si>
+    <t>2007/1/1</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>マミーズケア ＆サポート城下</t>
+  </si>
+  <si>
+    <t>城下 利香</t>
+  </si>
+  <si>
+    <t>香川県高松市牟礼町</t>
+  </si>
+  <si>
+    <t>2007/2/1</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>特定非営利活動法人いのちの応援舎ぼっこ助産院</t>
-  </si>
-  <si>
-    <t>理事長　松尾　真理</t>
-  </si>
-  <si>
-    <t>特定非営利活動法人いのちの応援舎　</t>
-  </si>
-  <si>
-    <t>34.332435</t>
-  </si>
-  <si>
-    <t>134.097244</t>
-  </si>
-  <si>
-    <t>香川県高松市春日町１１７６番地</t>
-  </si>
-  <si>
-    <t>087-844-4103</t>
-  </si>
-  <si>
-    <t>2007/1/1</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>○</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>マミーズケア ＆サポート城下</t>
-  </si>
-  <si>
-    <t>城下 利香</t>
-  </si>
-  <si>
-    <t>香川県高松市牟礼町</t>
-  </si>
-  <si>
-    <t>2007/2/1</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -214,7 +214,7 @@
     <t>134.01324</t>
   </si>
   <si>
-    <t>高松市円座町１３２２－１</t>
+    <t>高松市円座町１３２２−１</t>
   </si>
   <si>
     <t>2026/04/01</t>
@@ -365,6 +365,27 @@
   </si>
   <si>
     <t>2025/11/10</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>助産院ｓｅｔｏなぎのわ</t>
+  </si>
+  <si>
+    <t>吉見　有沙</t>
+  </si>
+  <si>
+    <t>34.322858</t>
+  </si>
+  <si>
+    <t>134.092481</t>
+  </si>
+  <si>
+    <t>高松市春日町４６８－２</t>
+  </si>
+  <si>
+    <t>2026/6/15</t>
   </si>
 </sst>
 </file>
@@ -408,7 +429,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -748,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
@@ -791,542 +812,570 @@
     </row>
     <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="L3" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="J4" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L5" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="I6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J6" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J7" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="J8" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I10" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="J10" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G12" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H12" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I12" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J12" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K12" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L12" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I13" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J13" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K13" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L13" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F14" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G14" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="J14" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K14" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L14" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" t="s">
+        <v>107</v>
+      </c>
+      <c r="J15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>108</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>109</v>
       </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
         <v>110</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E16" t="s">
         <v>111</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F16" t="s">
         <v>112</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G16" t="s">
         <v>113</v>
       </c>
-      <c r="H15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="H16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" t="s">
         <v>114</v>
       </c>
-      <c r="J15" t="s">
-        <v>13</v>
-      </c>
-      <c r="K15" t="s">
-        <v>12</v>
-      </c>
-      <c r="L15" t="s">
-        <v>12</v>
+      <c r="J16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L1 A2:L15" numberStoredAsText="1"/>
+    <ignoredError sqref="A3:L16 A1:L1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>